--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2132,6 +2132,525 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120488446</v>
+      </c>
+      <c r="B14" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ire klint, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>710280</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6415534</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120488441</v>
+      </c>
+      <c r="B15" t="n">
+        <v>86449</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ire klint, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>710300</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6415532</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120488850</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>710414</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6415689</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120488447</v>
+      </c>
+      <c r="B17" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ire klint, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>710304</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6415532</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120488444</v>
+      </c>
+      <c r="B18" t="n">
+        <v>106872</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ire klint, Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>710342</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6415553</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2134,10 +2134,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120488446</v>
+        <v>120488850</v>
       </c>
       <c r="B14" t="n">
-        <v>86373</v>
+        <v>100194</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2146,41 +2146,45 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>248956</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ire klint, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>710280</v>
+        <v>710414</v>
       </c>
       <c r="R14" t="n">
-        <v>6415534</v>
+        <v>6415689</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2218,28 +2222,33 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120488441</v>
+        <v>120488444</v>
       </c>
       <c r="B15" t="n">
-        <v>86449</v>
+        <v>106872</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2252,21 +2261,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2276,10 +2285,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>710300</v>
+        <v>710342</v>
       </c>
       <c r="R15" t="n">
-        <v>6415532</v>
+        <v>6415553</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2338,10 +2347,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120488850</v>
+        <v>120488441</v>
       </c>
       <c r="B16" t="n">
-        <v>100194</v>
+        <v>86449</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2350,45 +2359,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>6003295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Ire klint, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>710414</v>
+        <v>710300</v>
       </c>
       <c r="R16" t="n">
-        <v>6415689</v>
+        <v>6415532</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2426,26 +2431,21 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
-        </is>
-      </c>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2551,10 +2551,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120488444</v>
+        <v>120488446</v>
       </c>
       <c r="B18" t="n">
-        <v>106872</v>
+        <v>86373</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2563,25 +2563,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220079</v>
+        <v>248956</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>710342</v>
+        <v>710280</v>
       </c>
       <c r="R18" t="n">
-        <v>6415553</v>
+        <v>6415534</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2650,6 +2650,317 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120508019</v>
+      </c>
+      <c r="B19" t="n">
+        <v>86427</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>249228</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Barrfagerspindling</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ireklint, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>710585</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6415510</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120508016</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ireklint, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>710560</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6415348</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120508018</v>
+      </c>
+      <c r="B21" t="n">
+        <v>90878</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1973</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kristallporing</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Gelatoporia subvermispora</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Pilát) Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ireklint, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>710587</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6415458</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -2134,10 +2134,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120488850</v>
+        <v>120488444</v>
       </c>
       <c r="B14" t="n">
-        <v>100194</v>
+        <v>106872</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2146,45 +2146,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>220079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Ire klint, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>710414</v>
+        <v>710342</v>
       </c>
       <c r="R14" t="n">
-        <v>6415689</v>
+        <v>6415553</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2222,33 +2218,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
-        </is>
-      </c>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120488444</v>
+        <v>120488447</v>
       </c>
       <c r="B15" t="n">
-        <v>106872</v>
+        <v>86373</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2257,25 +2248,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220079</v>
+        <v>248956</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2285,10 +2276,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>710342</v>
+        <v>710304</v>
       </c>
       <c r="R15" t="n">
-        <v>6415553</v>
+        <v>6415532</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2347,10 +2338,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120488441</v>
+        <v>120488850</v>
       </c>
       <c r="B16" t="n">
-        <v>86449</v>
+        <v>100194</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2359,41 +2350,45 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6003295</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ire klint, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>710300</v>
+        <v>710414</v>
       </c>
       <c r="R16" t="n">
-        <v>6415532</v>
+        <v>6415689</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2431,28 +2426,33 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120488447</v>
+        <v>120488441</v>
       </c>
       <c r="B17" t="n">
-        <v>86373</v>
+        <v>86449</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2461,25 +2461,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>710304</v>
+        <v>710300</v>
       </c>
       <c r="R17" t="n">
         <v>6415532</v>
@@ -2653,10 +2653,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120508019</v>
+        <v>120508018</v>
       </c>
       <c r="B19" t="n">
-        <v>86427</v>
+        <v>90878</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2665,25 +2665,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>249228</v>
+        <v>1973</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Kristallporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Gelatoporia subvermispora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>(Pilát) Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>710585</v>
+        <v>710587</v>
       </c>
       <c r="R19" t="n">
-        <v>6415510</v>
+        <v>6415458</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2723,12 +2723,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2755,10 +2755,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120508016</v>
+        <v>120508019</v>
       </c>
       <c r="B20" t="n">
-        <v>57336</v>
+        <v>86427</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2767,38 +2767,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>249228</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ireklint, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>710560</v>
+        <v>710585</v>
       </c>
       <c r="R20" t="n">
-        <v>6415348</v>
+        <v>6415510</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2833,17 +2836,13 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2855,17 +2854,21 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Suvi Sivula, Dennis Nyström, Ola Elleström, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120508018</v>
+        <v>120508016</v>
       </c>
       <c r="B21" t="n">
-        <v>90878</v>
+        <v>57336</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2878,34 +2881,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1973</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kristallporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gelatoporia subvermispora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ireklint, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>710587</v>
+        <v>710560</v>
       </c>
       <c r="R21" t="n">
-        <v>6415458</v>
+        <v>6415348</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2932,12 +2947,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2957,10 +2972,14 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Suvi Sivula, Dennis Nyström, Ola Elleström, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -2134,10 +2134,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120488444</v>
+        <v>120488446</v>
       </c>
       <c r="B14" t="n">
-        <v>106872</v>
+        <v>86373</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2146,25 +2146,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220079</v>
+        <v>248956</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>710342</v>
+        <v>710280</v>
       </c>
       <c r="R14" t="n">
-        <v>6415553</v>
+        <v>6415534</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120488447</v>
+        <v>120488441</v>
       </c>
       <c r="B15" t="n">
-        <v>86373</v>
+        <v>86449</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2248,25 +2248,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>710304</v>
+        <v>710300</v>
       </c>
       <c r="R15" t="n">
         <v>6415532</v>
@@ -2338,10 +2338,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120488850</v>
+        <v>120488447</v>
       </c>
       <c r="B16" t="n">
-        <v>100194</v>
+        <v>86373</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2350,45 +2350,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>248956</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Ire klint, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>710414</v>
+        <v>710304</v>
       </c>
       <c r="R16" t="n">
-        <v>6415689</v>
+        <v>6415532</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2426,33 +2422,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
-        </is>
-      </c>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120488441</v>
+        <v>120488444</v>
       </c>
       <c r="B17" t="n">
-        <v>86449</v>
+        <v>106872</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2465,21 +2456,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2489,10 +2480,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>710300</v>
+        <v>710342</v>
       </c>
       <c r="R17" t="n">
-        <v>6415532</v>
+        <v>6415553</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2551,10 +2542,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120488446</v>
+        <v>120488850</v>
       </c>
       <c r="B18" t="n">
-        <v>86373</v>
+        <v>100194</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2563,41 +2554,45 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>248956</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ire klint, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>710280</v>
+        <v>710414</v>
       </c>
       <c r="R18" t="n">
-        <v>6415534</v>
+        <v>6415689</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2635,21 +2630,26 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Suvi Sivula, Dennis Nyström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -2010,12 +2010,7 @@
         <v>106587992</v>
       </c>
       <c r="B13" t="n">
-        <v>96361</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98607</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,10 +2042,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>710471.4629323657</v>
+        <v>710471</v>
       </c>
       <c r="R13" t="n">
-        <v>6415438.60498973</v>
+        <v>6415439</v>
       </c>
       <c r="S13" t="n">
         <v>71</v>
@@ -2080,19 +2075,9 @@
           <t>1993-07-02</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>1993-07-02</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -2010,7 +2010,7 @@
         <v>106587992</v>
       </c>
       <c r="B13" t="n">
-        <v>98607</v>
+        <v>98613</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -2010,7 +2010,7 @@
         <v>106587992</v>
       </c>
       <c r="B13" t="n">
-        <v>98613</v>
+        <v>98616</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -2010,7 +2010,7 @@
         <v>106587992</v>
       </c>
       <c r="B13" t="n">
-        <v>98616</v>
+        <v>98619</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -2010,7 +2010,7 @@
         <v>106587992</v>
       </c>
       <c r="B13" t="n">
-        <v>98619</v>
+        <v>98620</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -2010,7 +2010,7 @@
         <v>106587992</v>
       </c>
       <c r="B13" t="n">
-        <v>98620</v>
+        <v>98647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -2010,7 +2010,7 @@
         <v>106587992</v>
       </c>
       <c r="B13" t="n">
-        <v>98647</v>
+        <v>98653</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -2010,7 +2010,7 @@
         <v>106587992</v>
       </c>
       <c r="B13" t="n">
-        <v>98653</v>
+        <v>98660</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -2010,7 +2010,7 @@
         <v>106587992</v>
       </c>
       <c r="B13" t="n">
-        <v>98660</v>
+        <v>98664</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -2010,7 +2010,7 @@
         <v>106587992</v>
       </c>
       <c r="B13" t="n">
-        <v>98664</v>
+        <v>98671</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -2010,7 +2010,7 @@
         <v>106587992</v>
       </c>
       <c r="B13" t="n">
-        <v>98674</v>
+        <v>98679</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -2010,7 +2010,7 @@
         <v>106587992</v>
       </c>
       <c r="B13" t="n">
-        <v>98679</v>
+        <v>98687</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56872697</v>
+        <v>56872606</v>
       </c>
       <c r="B2" t="n">
-        <v>85148</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>710403.4817617844</v>
+        <v>710375</v>
       </c>
       <c r="R2" t="n">
-        <v>6415511.861812501</v>
+        <v>6415387</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2015-10-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-10-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,12 +784,7 @@
         <v>56872609</v>
       </c>
       <c r="B3" t="n">
-        <v>85125</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -845,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>710419.8226460078</v>
+        <v>710420</v>
       </c>
       <c r="R3" t="n">
-        <v>6415556.996804752</v>
+        <v>6415557</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,19 +858,9 @@
           <t>2015-10-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-10-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56872700</v>
+        <v>56872697</v>
       </c>
       <c r="B4" t="n">
-        <v>85148</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,17 +907,13 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>M. M. Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -966,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>710456.4325330232</v>
+        <v>710403</v>
       </c>
       <c r="R4" t="n">
-        <v>6415653.873116445</v>
+        <v>6415512</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,19 +960,9 @@
           <t>2015-10-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-10-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,15 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56872703</v>
+        <v>56872700</v>
       </c>
       <c r="B5" t="n">
-        <v>85148</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,17 +1009,13 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>M. M. Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1087,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>710457.5543532301</v>
+        <v>710456</v>
       </c>
       <c r="R5" t="n">
-        <v>6415652.865029997</v>
+        <v>6415654</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,19 +1062,9 @@
           <t>2015-10-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2015-10-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,15 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>56872833</v>
+        <v>56872703</v>
       </c>
       <c r="B6" t="n">
-        <v>85306</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,26 +1102,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>248939</v>
+        <v>433</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallpraktspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius terpsichores</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Melot</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1208,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>710403.4817617844</v>
+        <v>710458</v>
       </c>
       <c r="R6" t="n">
-        <v>6415511.861812501</v>
+        <v>6415653</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,28 +1164,17 @@
           <t>2015-10-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2015-10-10</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1284,12 +1196,7 @@
         <v>56872705</v>
       </c>
       <c r="B7" t="n">
-        <v>85148</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,14 +1213,10 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>M. M. Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>32</t>
@@ -1330,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>710471.7195578758</v>
+        <v>710472</v>
       </c>
       <c r="R7" t="n">
-        <v>6415647.739855651</v>
+        <v>6415648</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,19 +1266,9 @@
           <t>2015-10-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2015-10-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,15 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56872606</v>
+        <v>56872708</v>
       </c>
       <c r="B8" t="n">
-        <v>85125</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,26 +1306,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1451,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>710374.7715053606</v>
+        <v>710445</v>
       </c>
       <c r="R8" t="n">
-        <v>6415386.588514319</v>
+        <v>6415743</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1484,19 +1368,9 @@
           <t>2015-10-10</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2015-10-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,15 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>56872809</v>
+        <v>56872732</v>
       </c>
       <c r="B9" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,26 +1408,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>248956</v>
+        <v>433</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1572,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>710471.7195578758</v>
+        <v>710677</v>
       </c>
       <c r="R9" t="n">
-        <v>6415647.739855651</v>
+        <v>6415628</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1605,19 +1470,9 @@
           <t>2015-10-10</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2015-10-10</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1644,15 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>56872708</v>
+        <v>56872843</v>
       </c>
       <c r="B10" t="n">
-        <v>85148</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89164</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,26 +1510,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>433</v>
+        <v>826</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Lundvaxskivling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens</t>
+          <t>Hygrophorus nemoreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>(Pers.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1693,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>710445.3217069001</v>
+        <v>710420</v>
       </c>
       <c r="R10" t="n">
-        <v>6415743.443875692</v>
+        <v>6415557</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1726,19 +1576,9 @@
           <t>2015-10-10</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2015-10-10</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1765,59 +1605,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>56872732</v>
+        <v>120508018</v>
       </c>
       <c r="B11" t="n">
-        <v>85148</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92239</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>433</v>
+        <v>1973</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Kristallporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens</t>
+          <t>Gelatoporia subvermispora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pilát) Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stenkyrka, Gtl</t>
+          <t>Ireklint, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>710676.9219374354</v>
+        <v>710587</v>
       </c>
       <c r="R11" t="n">
-        <v>6415628.099587734</v>
+        <v>6415458</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1844,22 +1670,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2015-10-10</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2015-10-10</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1874,74 +1690,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
+          <t>Suvi Bergström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
+          <t>Suvi Bergström, Dennis Nyström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>56872843</v>
+        <v>96531476</v>
       </c>
       <c r="B12" t="n">
-        <v>86219</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>87333</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>826</v>
+        <v>3599</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lundvaxskivling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hygrophorus nemoreus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stenkyrka, Gtl</t>
+          <t>Stenkyrka Höglundarkusten, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>710419.8226460078</v>
+        <v>710237</v>
       </c>
       <c r="R12" t="n">
-        <v>6415556.996804752</v>
+        <v>6415897</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1965,22 +1767,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2015-10-10</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2015-10-10</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1989,28 +1781,38 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Moa Pettersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106587992</v>
+        <v>96531473</v>
       </c>
       <c r="B13" t="n">
-        <v>98687</v>
+        <v>91322</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,37 +1820,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219864</v>
+        <v>4188</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grausne källmyr ca 700 m NO, Gtl</t>
+          <t>Stenkyrka Höglundarkusten, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>710471</v>
+        <v>710237</v>
       </c>
       <c r="R13" t="n">
-        <v>6415439</v>
+        <v>6415897</v>
       </c>
       <c r="S13" t="n">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2072,12 +1874,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>1993-07-02</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1993-07-02</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2091,78 +1893,79 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Tallskog, torr gräsrik</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr"/>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Thomas Karlsson</t>
+          <t>Moa Pettersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>Projekt Gotlands Flora</t>
+          <t>SMF:s mykologivecka</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120488444</v>
+        <v>120508016</v>
       </c>
       <c r="B14" t="n">
-        <v>106990</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220079</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ire klint, Gtl</t>
+          <t>Ireklint, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>710342</v>
+        <v>710560</v>
       </c>
       <c r="R14" t="n">
-        <v>6415553</v>
+        <v>6415348</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2209,65 +2012,64 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Suvi Bergström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Suvi Bergström, Dennis Nyström, Ola Elleström, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120488446</v>
+        <v>106587992</v>
       </c>
       <c r="B15" t="n">
-        <v>86177</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>248956</v>
+        <v>219864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ire klint, Gtl</t>
+          <t>Grausne källmyr ca 700 m NO, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>710280</v>
+        <v>710471</v>
       </c>
       <c r="R15" t="n">
-        <v>6415534</v>
+        <v>6415439</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2291,12 +2093,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>1993-07-02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>1993-07-02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2308,30 +2110,40 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Tallskog, torr gräsrik</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr"/>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120488441</v>
+        <v>120488444</v>
       </c>
       <c r="B16" t="n">
-        <v>86254</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,21 +2151,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2363,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>710300</v>
+        <v>710342</v>
       </c>
       <c r="R16" t="n">
-        <v>6415532</v>
+        <v>6415553</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2425,57 +2237,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120488850</v>
+        <v>106587996</v>
       </c>
       <c r="B17" t="n">
-        <v>100311</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102560</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>222133</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Grausne källmyr ca 700 m NO, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>710414</v>
+        <v>710471</v>
       </c>
       <c r="R17" t="n">
-        <v>6415689</v>
+        <v>6415439</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2499,12 +2302,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>1993-07-02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>1993-07-02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,76 +2316,85 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Tallskog, torr, vid körspår.</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr"/>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Thomas Karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
+          <t>Projekt Gotlands Flora</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120488447</v>
+        <v>120488850</v>
       </c>
       <c r="B18" t="n">
-        <v>86177</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>248956</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ire klint, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>710304</v>
+        <v>710414</v>
       </c>
       <c r="R18" t="n">
-        <v>6415532</v>
+        <v>6415689</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2620,68 +2432,77 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120508018</v>
+        <v>56872833</v>
       </c>
       <c r="B19" t="n">
-        <v>90980</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87380</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1973</v>
+        <v>248939</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kristallporing</t>
+          <t>Tallpraktspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gelatoporia subvermispora</t>
+          <t>Cortinarius terpsichores</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Melot</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ireklint, Gtl</t>
+          <t>Stenkyrka, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>710587</v>
+        <v>710403</v>
       </c>
       <c r="R19" t="n">
-        <v>6415458</v>
+        <v>6415512</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2708,12 +2529,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2015-10-10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2015-10-10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2722,71 +2543,73 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Åke Edvinsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Dennis Nyström</t>
+          <t>Åke Edvinsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120508019</v>
+        <v>56872809</v>
       </c>
       <c r="B20" t="n">
-        <v>86232</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87262</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>249228</v>
+        <v>248956</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ireklint, Gtl</t>
+          <t>Stenkyrka, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>710585</v>
+        <v>710472</v>
       </c>
       <c r="R20" t="n">
-        <v>6415510</v>
+        <v>6415648</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2813,12 +2636,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2015-10-10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2015-10-10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2827,85 +2650,63 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Åke Edvinsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Dennis Nyström, Ola Elleström, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
-        </is>
-      </c>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120508016</v>
+        <v>120488446</v>
       </c>
       <c r="B21" t="n">
-        <v>57364</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87262</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>248956</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ireklint, Gtl</t>
+          <t>Ire klint, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>710560</v>
+        <v>710280</v>
       </c>
       <c r="R21" t="n">
-        <v>6415348</v>
+        <v>6415534</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2952,19 +2753,314 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Dennis Nyström, Ola Elleström, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120488447</v>
+      </c>
+      <c r="B22" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ire klint, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>710304</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6415532</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120508019</v>
+      </c>
+      <c r="B23" t="n">
+        <v>87323</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>249228</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Barrfagerspindling</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ireklint, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>710585</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6415510</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Suvi Bergström, Dennis Nyström, Ola Elleström, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
         <is>
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120488441</v>
+      </c>
+      <c r="B24" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ire klint, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>710300</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6415532</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56872606</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56872609</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56872697</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56872700</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1190,6 +1215,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56872703</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,6 +1322,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56872705</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56872708</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56872732</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1602,6 +1647,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56872843</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1699,6 +1749,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120508018</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1806,6 +1861,11 @@
           <t>SMF:s mykologivecka</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96531476</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1912,6 +1972,11 @@
           <t>SMF:s mykologivecka</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96531473</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2025,6 +2090,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120508016</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2137,6 +2207,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106587992</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2234,6 +2309,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488444</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2344,6 +2424,11 @@
       <c r="AY17" t="inlineStr">
         <is>
           <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106587996</t>
         </is>
       </c>
     </row>
@@ -2452,6 +2537,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488850</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2559,6 +2649,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56872833</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2665,6 +2760,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56872809</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2762,6 +2862,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488446</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2859,6 +2964,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488447</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2964,6 +3074,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120508019</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3061,8 +3176,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488441</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2098,48 +2098,72 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>106587992</v>
+        <v>135651157</v>
       </c>
       <c r="B15" t="n">
-        <v>99147</v>
+        <v>43309</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219864</v>
+        <v>101260</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Grausne källmyr ca 700 m NO, Gtl</t>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>710471</v>
+        <v>710357</v>
       </c>
       <c r="R15" t="n">
-        <v>6415439</v>
+        <v>6415717</v>
       </c>
       <c r="S15" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2163,12 +2187,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>1993-07-02</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1993-07-02</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2182,15 +2206,9 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Tallskog, torr gräsrik</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr"/>
+          <t>Kalktallskog med vissa tuvor av backtimjan.</t>
+        </is>
+      </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
@@ -2199,64 +2217,60 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Thomas Karlsson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106587992</t>
+          <t>https://artportalen.se/Sighting/135651157</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120488444</v>
+        <v>106587992</v>
       </c>
       <c r="B16" t="n">
-        <v>108116</v>
+        <v>99147</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ire klint, Gtl</t>
+          <t>Grausne källmyr ca 700 m NO, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>710342</v>
+        <v>710471</v>
       </c>
       <c r="R16" t="n">
-        <v>6415553</v>
+        <v>6415439</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2280,12 +2294,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>1993-07-02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>1993-07-02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2297,30 +2311,45 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Tallskog, torr gräsrik</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr"/>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120488444</t>
+          <t>https://artportalen.se/Sighting/106587992</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>106587996</v>
+        <v>120488444</v>
       </c>
       <c r="B17" t="n">
-        <v>102560</v>
+        <v>108116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2328,37 +2357,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222133</v>
+        <v>220079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grausne källmyr ca 700 m NO, Gtl</t>
+          <t>Ire klint, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>710471</v>
+        <v>710342</v>
       </c>
       <c r="R17" t="n">
-        <v>6415439</v>
+        <v>6415553</v>
       </c>
       <c r="S17" t="n">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2382,12 +2411,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>1993-07-02</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1993-07-02</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2399,87 +2428,77 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Tallskog, torr, vid körspår.</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr"/>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Thomas Karlsson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106587996</t>
+          <t>https://artportalen.se/Sighting/120488444</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120488850</v>
+        <v>135650961</v>
       </c>
       <c r="B18" t="n">
-        <v>101326</v>
+        <v>108252</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>220079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>710414</v>
+        <v>710527</v>
       </c>
       <c r="R18" t="n">
-        <v>6415689</v>
+        <v>6415432</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2503,12 +2522,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,85 +2536,85 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Kalktallskog, kalkglänta vid nyanlagdf kalkgrusväg (timmerupplagsplats?).</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120488850</t>
+          <t>https://artportalen.se/Sighting/135650961</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>56872833</v>
+        <v>135650968</v>
       </c>
       <c r="B19" t="n">
-        <v>87380</v>
+        <v>108252</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>248939</v>
+        <v>220079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallpraktspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius terpsichores</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Melot</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stenkyrka, Gtl</t>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>710403</v>
+        <v>710567</v>
       </c>
       <c r="R19" t="n">
-        <v>6415512</v>
+        <v>6415523</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2619,12 +2638,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2015-10-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2015-10-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2633,81 +2652,85 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Kalktallskog.</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56872833</t>
+          <t>https://artportalen.se/Sighting/135650968</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>56872809</v>
+        <v>135650972</v>
       </c>
       <c r="B20" t="n">
-        <v>87262</v>
+        <v>108252</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>248956</v>
+        <v>220079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stenkyrka, Gtl</t>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>710472</v>
+        <v>710515</v>
       </c>
       <c r="R20" t="n">
-        <v>6415648</v>
+        <v>6415629</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2731,12 +2754,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2015-10-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2015-10-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2747,66 +2770,80 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Kalktallskog gles, delvis röjd (plockhuggen?).</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56872809</t>
+          <t>https://artportalen.se/Sighting/135650972</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120488446</v>
+        <v>135651005</v>
       </c>
       <c r="B21" t="n">
-        <v>87262</v>
+        <v>108252</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>248956</v>
+        <v>220079</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ire klint, Gtl</t>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>710280</v>
+        <v>710497</v>
       </c>
       <c r="R21" t="n">
-        <v>6415534</v>
+        <v>6415364</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2833,12 +2870,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2849,69 +2886,83 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog i kalkglänta.</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120488446</t>
+          <t>https://artportalen.se/Sighting/135651005</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120488447</v>
+        <v>135650965</v>
       </c>
       <c r="B22" t="n">
-        <v>87262</v>
+        <v>110215</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>248956</v>
+        <v>220299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ire klint, Gtl</t>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>710304</v>
+        <v>710575</v>
       </c>
       <c r="R22" t="n">
-        <v>6415532</v>
+        <v>6415480</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2935,12 +2986,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2951,31 +3002,36 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Kalktallskog.</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120488447</t>
+          <t>https://artportalen.se/Sighting/135650965</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120508019</v>
+        <v>135650976</v>
       </c>
       <c r="B23" t="n">
-        <v>87323</v>
+        <v>110215</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2983,40 +3039,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>249228</v>
+        <v>220299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ireklint, Gtl</t>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>710585</v>
+        <v>710489</v>
       </c>
       <c r="R23" t="n">
-        <v>6415510</v>
+        <v>6415639</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3040,12 +3093,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3054,38 +3107,38 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Kalktallskog gles, delvis röjd (plockhuggen?).</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Suvi Bergström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Suvi Bergström, Dennis Nyström, Ola Elleström, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120508019</t>
+          <t>https://artportalen.se/Sighting/135650976</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120488441</v>
+        <v>135650979</v>
       </c>
       <c r="B24" t="n">
-        <v>87346</v>
+        <v>110215</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3093,37 +3146,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6003295</v>
+        <v>220299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ire klint, Gtl</t>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>710300</v>
+        <v>710464</v>
       </c>
       <c r="R24" t="n">
-        <v>6415532</v>
+        <v>6415639</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3147,12 +3209,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3163,20 +3225,2667 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Kalktallskog gles, delvis röjd (plockhuggen?).</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650979</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135650983</v>
+      </c>
+      <c r="B25" t="n">
+        <v>110215</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>710303</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6415682</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Kalktallskog gles, delvis röjd (plockhuggen?).</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650983</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135650987</v>
+      </c>
+      <c r="B26" t="n">
+        <v>110215</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>710305</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6415517</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalktallskog.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650987</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135650967</v>
+      </c>
+      <c r="B27" t="n">
+        <v>107653</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>710597</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6415507</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Röjt område O östra nya körvägen; även avverkade träd.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalktallskog gles, delvis röjd (plockhuggen?).</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650967</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135650969</v>
+      </c>
+      <c r="B28" t="n">
+        <v>107653</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>710567</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6415523</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kalktallskog.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650969</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135650970</v>
+      </c>
+      <c r="B29" t="n">
+        <v>107653</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>710591</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6415547</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Spridd. Skog troligen opåverkad av skogsbruk.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kalktallskog.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650970</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135650973</v>
+      </c>
+      <c r="B30" t="n">
+        <v>107653</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>710515</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6415629</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalktallskog gles, delvis röjd (plockhuggen?).</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650973</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135650974</v>
+      </c>
+      <c r="B31" t="n">
+        <v>107653</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>710489</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6415639</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalktallskog gles, delvis röjd (plockhuggen?).</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650974</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135650980</v>
+      </c>
+      <c r="B32" t="n">
+        <v>107653</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>710450</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6415712</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Kalktallskog gles, delvis röjd (plockhuggen?).</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650980</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135650982</v>
+      </c>
+      <c r="B33" t="n">
+        <v>107653</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>710357</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6415717</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Några tuvor.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalktallskog gles, delvis röjd (plockhuggen?).</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650982</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135650986</v>
+      </c>
+      <c r="B34" t="n">
+        <v>107653</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>710284</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6415676</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Just V stig.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalktallskog gles, delvis röjd (plockhuggen?).</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650986</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135650998</v>
+      </c>
+      <c r="B35" t="n">
+        <v>107653</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>710389</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6415495</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalktallskog gles, delvis röjd (plockhuggen?).</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650998</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135650999</v>
+      </c>
+      <c r="B36" t="n">
+        <v>107653</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>710381</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6415471</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalktallskog gles, delvis röjd (plockhuggen?).</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650999</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135651002</v>
+      </c>
+      <c r="B37" t="n">
+        <v>107653</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>710404</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6415434</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135651002</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135651003</v>
+      </c>
+      <c r="B38" t="n">
+        <v>107653</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>710428</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6415418</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135651003</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135651004</v>
+      </c>
+      <c r="B39" t="n">
+        <v>107653</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>710427</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6415402</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135651004</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135651008</v>
+      </c>
+      <c r="B40" t="n">
+        <v>107653</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>710497</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6415364</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog i kalkglänta.</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135651008</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>106587996</v>
+      </c>
+      <c r="B41" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Grausne källmyr ca 700 m NO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>710471</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6415439</v>
+      </c>
+      <c r="S41" t="n">
+        <v>71</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>1993-07-02</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>1993-07-02</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Tallskog, torr, vid körspår.</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106587996</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120488850</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>710414</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6415689</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488850</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>56872833</v>
+      </c>
+      <c r="B43" t="n">
+        <v>87380</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>248939</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tallpraktspindling</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Cortinarius terpsichores</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Melot</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stenkyrka, Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>710403</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6415512</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2015-10-10</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2015-10-10</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56872833</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>56872809</v>
+      </c>
+      <c r="B44" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stenkyrka, Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>710472</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6415648</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2015-10-10</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2015-10-10</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56872809</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120488446</v>
+      </c>
+      <c r="B45" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Ire klint, Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>710280</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6415534</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488446</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120488447</v>
+      </c>
+      <c r="B46" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Ire klint, Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>710304</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6415532</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488447</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120508019</v>
+      </c>
+      <c r="B47" t="n">
+        <v>87323</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>249228</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Barrfagerspindling</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Ireklint, Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>710585</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6415510</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Suvi Bergström, Dennis Nyström, Ola Elleström, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120508019</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120488441</v>
+      </c>
+      <c r="B48" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Ire klint, Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>710300</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6415532</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/120488441</t>
         </is>
@@ -3207,6 +5916,30 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -2451,7 +2451,7 @@
         <v>135650961</v>
       </c>
       <c r="B18" t="n">
-        <v>108252</v>
+        <v>108279</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>135650968</v>
       </c>
       <c r="B19" t="n">
-        <v>108252</v>
+        <v>108279</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>135650972</v>
       </c>
       <c r="B20" t="n">
-        <v>108252</v>
+        <v>108279</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>135651005</v>
       </c>
       <c r="B21" t="n">
-        <v>108252</v>
+        <v>108279</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>135650965</v>
       </c>
       <c r="B22" t="n">
-        <v>110215</v>
+        <v>110242</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>135650976</v>
       </c>
       <c r="B23" t="n">
-        <v>110215</v>
+        <v>110242</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>135650979</v>
       </c>
       <c r="B24" t="n">
-        <v>110215</v>
+        <v>110242</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>135650983</v>
       </c>
       <c r="B25" t="n">
-        <v>110215</v>
+        <v>110242</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>135650987</v>
       </c>
       <c r="B26" t="n">
-        <v>110215</v>
+        <v>110242</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>135650967</v>
       </c>
       <c r="B27" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>135650969</v>
       </c>
       <c r="B28" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>135650970</v>
       </c>
       <c r="B29" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>135650973</v>
       </c>
       <c r="B30" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>135650974</v>
       </c>
       <c r="B31" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>135650980</v>
       </c>
       <c r="B32" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>135650982</v>
       </c>
       <c r="B33" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>135650986</v>
       </c>
       <c r="B34" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>135650998</v>
       </c>
       <c r="B35" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>135650999</v>
       </c>
       <c r="B36" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>135651002</v>
       </c>
       <c r="B37" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>135651003</v>
       </c>
       <c r="B38" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>135651004</v>
       </c>
       <c r="B39" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>135651008</v>
       </c>
       <c r="B40" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2098,48 +2098,72 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>106587992</v>
+        <v>135651157</v>
       </c>
       <c r="B15" t="n">
-        <v>99147</v>
+        <v>43309</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219864</v>
+        <v>101260</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Grausne källmyr ca 700 m NO, Gtl</t>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>710471</v>
+        <v>710357</v>
       </c>
       <c r="R15" t="n">
-        <v>6415439</v>
+        <v>6415717</v>
       </c>
       <c r="S15" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2163,12 +2187,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>1993-07-02</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1993-07-02</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2182,15 +2206,9 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Tallskog, torr gräsrik</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr"/>
+          <t>Kalktallskog med vissa tuvor av backtimjan.</t>
+        </is>
+      </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
@@ -2199,64 +2217,60 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Thomas Karlsson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106587992</t>
+          <t>https://artportalen.se/Sighting/135651157</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120488444</v>
+        <v>106587992</v>
       </c>
       <c r="B16" t="n">
-        <v>108116</v>
+        <v>99147</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ire klint, Gtl</t>
+          <t>Grausne källmyr ca 700 m NO, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>710342</v>
+        <v>710471</v>
       </c>
       <c r="R16" t="n">
-        <v>6415553</v>
+        <v>6415439</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2280,12 +2294,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>1993-07-02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>1993-07-02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2297,30 +2311,45 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Tallskog, torr gräsrik</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr"/>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120488444</t>
+          <t>https://artportalen.se/Sighting/106587992</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>106587996</v>
+        <v>120488444</v>
       </c>
       <c r="B17" t="n">
-        <v>102560</v>
+        <v>108116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2328,37 +2357,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222133</v>
+        <v>220079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grausne källmyr ca 700 m NO, Gtl</t>
+          <t>Ire klint, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>710471</v>
+        <v>710342</v>
       </c>
       <c r="R17" t="n">
-        <v>6415439</v>
+        <v>6415553</v>
       </c>
       <c r="S17" t="n">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2382,12 +2411,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>1993-07-02</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1993-07-02</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2399,87 +2428,77 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Tallskog, torr, vid körspår.</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr"/>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Thomas Karlsson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106587996</t>
+          <t>https://artportalen.se/Sighting/120488444</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120488850</v>
+        <v>135650961</v>
       </c>
       <c r="B18" t="n">
-        <v>101326</v>
+        <v>108284</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>220079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>710414</v>
+        <v>710527</v>
       </c>
       <c r="R18" t="n">
-        <v>6415689</v>
+        <v>6415432</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2503,12 +2522,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,85 +2536,85 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Kalktallskog, kalkglänta vid nyanlagdf kalkgrusväg (timmerupplagsplats?).</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120488850</t>
+          <t>https://artportalen.se/Sighting/135650961</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>56872833</v>
+        <v>135650968</v>
       </c>
       <c r="B19" t="n">
-        <v>87380</v>
+        <v>108284</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>248939</v>
+        <v>220079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallpraktspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius terpsichores</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Melot</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stenkyrka, Gtl</t>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>710403</v>
+        <v>710567</v>
       </c>
       <c r="R19" t="n">
-        <v>6415512</v>
+        <v>6415523</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2619,12 +2638,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2015-10-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2015-10-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2633,81 +2652,85 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Kalktallskog.</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56872833</t>
+          <t>https://artportalen.se/Sighting/135650968</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>56872809</v>
+        <v>135650972</v>
       </c>
       <c r="B20" t="n">
-        <v>87262</v>
+        <v>108284</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>248956</v>
+        <v>220079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stenkyrka, Gtl</t>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>710472</v>
+        <v>710515</v>
       </c>
       <c r="R20" t="n">
-        <v>6415648</v>
+        <v>6415629</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2731,12 +2754,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2015-10-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2015-10-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2747,66 +2770,80 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Kalktallskog gles, delvis röjd (plockhuggen?).</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56872809</t>
+          <t>https://artportalen.se/Sighting/135650972</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120488446</v>
+        <v>135651005</v>
       </c>
       <c r="B21" t="n">
-        <v>87262</v>
+        <v>108284</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>248956</v>
+        <v>220079</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ire klint, Gtl</t>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>710280</v>
+        <v>710497</v>
       </c>
       <c r="R21" t="n">
-        <v>6415534</v>
+        <v>6415364</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2833,12 +2870,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2849,69 +2886,83 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog i kalkglänta.</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120488446</t>
+          <t>https://artportalen.se/Sighting/135651005</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120488447</v>
+        <v>135650965</v>
       </c>
       <c r="B22" t="n">
-        <v>87262</v>
+        <v>110247</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>248956</v>
+        <v>220299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ire klint, Gtl</t>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>710304</v>
+        <v>710575</v>
       </c>
       <c r="R22" t="n">
-        <v>6415532</v>
+        <v>6415480</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2935,12 +2986,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2951,31 +3002,36 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Kalktallskog.</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120488447</t>
+          <t>https://artportalen.se/Sighting/135650965</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120508019</v>
+        <v>135650976</v>
       </c>
       <c r="B23" t="n">
-        <v>87323</v>
+        <v>110247</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2983,40 +3039,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>249228</v>
+        <v>220299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ireklint, Gtl</t>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>710585</v>
+        <v>710489</v>
       </c>
       <c r="R23" t="n">
-        <v>6415510</v>
+        <v>6415639</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3040,12 +3093,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3054,38 +3107,38 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Kalktallskog gles, delvis röjd (plockhuggen?).</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Suvi Bergström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Suvi Bergström, Dennis Nyström, Ola Elleström, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120508019</t>
+          <t>https://artportalen.se/Sighting/135650976</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120488441</v>
+        <v>135650979</v>
       </c>
       <c r="B24" t="n">
-        <v>87346</v>
+        <v>110247</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3093,37 +3146,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6003295</v>
+        <v>220299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ire klint, Gtl</t>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>710300</v>
+        <v>710464</v>
       </c>
       <c r="R24" t="n">
-        <v>6415532</v>
+        <v>6415639</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3147,12 +3209,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3163,20 +3225,2667 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Kalktallskog gles, delvis röjd (plockhuggen?).</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650979</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135650983</v>
+      </c>
+      <c r="B25" t="n">
+        <v>110247</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>710303</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6415682</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Kalktallskog gles, delvis röjd (plockhuggen?).</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650983</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135650987</v>
+      </c>
+      <c r="B26" t="n">
+        <v>110247</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>710305</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6415517</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalktallskog.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650987</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135650967</v>
+      </c>
+      <c r="B27" t="n">
+        <v>107685</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>710597</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6415507</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Röjt område O östra nya körvägen; även avverkade träd.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalktallskog gles, delvis röjd (plockhuggen?).</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650967</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135650969</v>
+      </c>
+      <c r="B28" t="n">
+        <v>107685</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>710567</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6415523</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kalktallskog.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650969</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135650970</v>
+      </c>
+      <c r="B29" t="n">
+        <v>107685</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>710591</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6415547</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Spridd. Skog troligen opåverkad av skogsbruk.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kalktallskog.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650970</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135650973</v>
+      </c>
+      <c r="B30" t="n">
+        <v>107685</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>710515</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6415629</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalktallskog gles, delvis röjd (plockhuggen?).</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650973</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135650974</v>
+      </c>
+      <c r="B31" t="n">
+        <v>107685</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>710489</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6415639</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalktallskog gles, delvis röjd (plockhuggen?).</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650974</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135650980</v>
+      </c>
+      <c r="B32" t="n">
+        <v>107685</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>710450</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6415712</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Kalktallskog gles, delvis röjd (plockhuggen?).</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650980</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135650982</v>
+      </c>
+      <c r="B33" t="n">
+        <v>107685</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>710357</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6415717</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Några tuvor.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalktallskog gles, delvis röjd (plockhuggen?).</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650982</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135650986</v>
+      </c>
+      <c r="B34" t="n">
+        <v>107685</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>710284</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6415676</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Just V stig.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalktallskog gles, delvis röjd (plockhuggen?).</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650986</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135650998</v>
+      </c>
+      <c r="B35" t="n">
+        <v>107685</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>710389</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6415495</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalktallskog gles, delvis röjd (plockhuggen?).</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650998</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135650999</v>
+      </c>
+      <c r="B36" t="n">
+        <v>107685</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>710381</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6415471</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalktallskog gles, delvis röjd (plockhuggen?).</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650999</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135651002</v>
+      </c>
+      <c r="B37" t="n">
+        <v>107685</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>710404</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6415434</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135651002</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135651003</v>
+      </c>
+      <c r="B38" t="n">
+        <v>107685</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>710428</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6415418</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135651003</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135651004</v>
+      </c>
+      <c r="B39" t="n">
+        <v>107685</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>710427</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6415402</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135651004</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135651008</v>
+      </c>
+      <c r="B40" t="n">
+        <v>107685</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stenkyrka Garde 1:5 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>710497</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6415364</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog i kalkglänta.</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135651008</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>106587996</v>
+      </c>
+      <c r="B41" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Grausne källmyr ca 700 m NO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>710471</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6415439</v>
+      </c>
+      <c r="S41" t="n">
+        <v>71</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>1993-07-02</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>1993-07-02</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Tallskog, torr, vid körspår.</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106587996</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120488850</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>710414</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6415689</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488850</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>56872833</v>
+      </c>
+      <c r="B43" t="n">
+        <v>87380</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>248939</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tallpraktspindling</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Cortinarius terpsichores</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Melot</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stenkyrka, Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>710403</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6415512</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2015-10-10</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2015-10-10</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56872833</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>56872809</v>
+      </c>
+      <c r="B44" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stenkyrka, Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>710472</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6415648</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2015-10-10</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2015-10-10</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56872809</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120488446</v>
+      </c>
+      <c r="B45" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Ire klint, Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>710280</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6415534</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488446</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120488447</v>
+      </c>
+      <c r="B46" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Ire klint, Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>710304</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6415532</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488447</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120508019</v>
+      </c>
+      <c r="B47" t="n">
+        <v>87323</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>249228</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Barrfagerspindling</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Ireklint, Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>710585</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6415510</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Suvi Bergström, Dennis Nyström, Ola Elleström, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120508019</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120488441</v>
+      </c>
+      <c r="B48" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Ire klint, Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>710300</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6415532</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/120488441</t>
         </is>
@@ -3207,6 +5916,30 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -2451,7 +2451,7 @@
         <v>135650961</v>
       </c>
       <c r="B18" t="n">
-        <v>108284</v>
+        <v>108286</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>135650968</v>
       </c>
       <c r="B19" t="n">
-        <v>108284</v>
+        <v>108286</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>135650972</v>
       </c>
       <c r="B20" t="n">
-        <v>108284</v>
+        <v>108286</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>135651005</v>
       </c>
       <c r="B21" t="n">
-        <v>108284</v>
+        <v>108286</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>135650965</v>
       </c>
       <c r="B22" t="n">
-        <v>110247</v>
+        <v>110249</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>135650976</v>
       </c>
       <c r="B23" t="n">
-        <v>110247</v>
+        <v>110249</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>135650979</v>
       </c>
       <c r="B24" t="n">
-        <v>110247</v>
+        <v>110249</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>135650983</v>
       </c>
       <c r="B25" t="n">
-        <v>110247</v>
+        <v>110249</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>135650987</v>
       </c>
       <c r="B26" t="n">
-        <v>110247</v>
+        <v>110249</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>135650967</v>
       </c>
       <c r="B27" t="n">
-        <v>107685</v>
+        <v>107687</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>135650969</v>
       </c>
       <c r="B28" t="n">
-        <v>107685</v>
+        <v>107687</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>135650970</v>
       </c>
       <c r="B29" t="n">
-        <v>107685</v>
+        <v>107687</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>135650973</v>
       </c>
       <c r="B30" t="n">
-        <v>107685</v>
+        <v>107687</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>135650974</v>
       </c>
       <c r="B31" t="n">
-        <v>107685</v>
+        <v>107687</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>135650980</v>
       </c>
       <c r="B32" t="n">
-        <v>107685</v>
+        <v>107687</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>135650982</v>
       </c>
       <c r="B33" t="n">
-        <v>107685</v>
+        <v>107687</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>135650986</v>
       </c>
       <c r="B34" t="n">
-        <v>107685</v>
+        <v>107687</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>135650998</v>
       </c>
       <c r="B35" t="n">
-        <v>107685</v>
+        <v>107687</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>135650999</v>
       </c>
       <c r="B36" t="n">
-        <v>107685</v>
+        <v>107687</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>135651002</v>
       </c>
       <c r="B37" t="n">
-        <v>107685</v>
+        <v>107687</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>135651003</v>
       </c>
       <c r="B38" t="n">
-        <v>107685</v>
+        <v>107687</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>135651004</v>
       </c>
       <c r="B39" t="n">
-        <v>107685</v>
+        <v>107687</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>135651008</v>
       </c>
       <c r="B40" t="n">
-        <v>107685</v>
+        <v>107687</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -2101,7 +2101,7 @@
         <v>135651157</v>
       </c>
       <c r="B15" t="n">
-        <v>43309</v>
+        <v>43311</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>135650961</v>
       </c>
       <c r="B18" t="n">
-        <v>108286</v>
+        <v>108309</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>135650968</v>
       </c>
       <c r="B19" t="n">
-        <v>108286</v>
+        <v>108309</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>135650972</v>
       </c>
       <c r="B20" t="n">
-        <v>108286</v>
+        <v>108309</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>135651005</v>
       </c>
       <c r="B21" t="n">
-        <v>108286</v>
+        <v>108309</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>135650965</v>
       </c>
       <c r="B22" t="n">
-        <v>110249</v>
+        <v>110272</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>135650976</v>
       </c>
       <c r="B23" t="n">
-        <v>110249</v>
+        <v>110272</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>135650979</v>
       </c>
       <c r="B24" t="n">
-        <v>110249</v>
+        <v>110272</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>135650983</v>
       </c>
       <c r="B25" t="n">
-        <v>110249</v>
+        <v>110272</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>135650987</v>
       </c>
       <c r="B26" t="n">
-        <v>110249</v>
+        <v>110272</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>135650967</v>
       </c>
       <c r="B27" t="n">
-        <v>107687</v>
+        <v>107710</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>135650969</v>
       </c>
       <c r="B28" t="n">
-        <v>107687</v>
+        <v>107710</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>135650970</v>
       </c>
       <c r="B29" t="n">
-        <v>107687</v>
+        <v>107710</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>135650973</v>
       </c>
       <c r="B30" t="n">
-        <v>107687</v>
+        <v>107710</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>135650974</v>
       </c>
       <c r="B31" t="n">
-        <v>107687</v>
+        <v>107710</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>135650980</v>
       </c>
       <c r="B32" t="n">
-        <v>107687</v>
+        <v>107710</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>135650982</v>
       </c>
       <c r="B33" t="n">
-        <v>107687</v>
+        <v>107710</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>135650986</v>
       </c>
       <c r="B34" t="n">
-        <v>107687</v>
+        <v>107710</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>135650998</v>
       </c>
       <c r="B35" t="n">
-        <v>107687</v>
+        <v>107710</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>135650999</v>
       </c>
       <c r="B36" t="n">
-        <v>107687</v>
+        <v>107710</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>135651002</v>
       </c>
       <c r="B37" t="n">
-        <v>107687</v>
+        <v>107710</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>135651003</v>
       </c>
       <c r="B38" t="n">
-        <v>107687</v>
+        <v>107710</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>135651004</v>
       </c>
       <c r="B39" t="n">
-        <v>107687</v>
+        <v>107710</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>135651008</v>
       </c>
       <c r="B40" t="n">
-        <v>107687</v>
+        <v>107710</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -2451,7 +2451,7 @@
         <v>135650961</v>
       </c>
       <c r="B18" t="n">
-        <v>108309</v>
+        <v>108311</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>135650968</v>
       </c>
       <c r="B19" t="n">
-        <v>108309</v>
+        <v>108311</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>135650972</v>
       </c>
       <c r="B20" t="n">
-        <v>108309</v>
+        <v>108311</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>135651005</v>
       </c>
       <c r="B21" t="n">
-        <v>108309</v>
+        <v>108311</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>135650965</v>
       </c>
       <c r="B22" t="n">
-        <v>110272</v>
+        <v>110274</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>135650976</v>
       </c>
       <c r="B23" t="n">
-        <v>110272</v>
+        <v>110274</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>135650979</v>
       </c>
       <c r="B24" t="n">
-        <v>110272</v>
+        <v>110274</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>135650983</v>
       </c>
       <c r="B25" t="n">
-        <v>110272</v>
+        <v>110274</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>135650987</v>
       </c>
       <c r="B26" t="n">
-        <v>110272</v>
+        <v>110274</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>135650967</v>
       </c>
       <c r="B27" t="n">
-        <v>107710</v>
+        <v>107712</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>135650969</v>
       </c>
       <c r="B28" t="n">
-        <v>107710</v>
+        <v>107712</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>135650970</v>
       </c>
       <c r="B29" t="n">
-        <v>107710</v>
+        <v>107712</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>135650973</v>
       </c>
       <c r="B30" t="n">
-        <v>107710</v>
+        <v>107712</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>135650974</v>
       </c>
       <c r="B31" t="n">
-        <v>107710</v>
+        <v>107712</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>135650980</v>
       </c>
       <c r="B32" t="n">
-        <v>107710</v>
+        <v>107712</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>135650982</v>
       </c>
       <c r="B33" t="n">
-        <v>107710</v>
+        <v>107712</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>135650986</v>
       </c>
       <c r="B34" t="n">
-        <v>107710</v>
+        <v>107712</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>135650998</v>
       </c>
       <c r="B35" t="n">
-        <v>107710</v>
+        <v>107712</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>135650999</v>
       </c>
       <c r="B36" t="n">
-        <v>107710</v>
+        <v>107712</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>135651002</v>
       </c>
       <c r="B37" t="n">
-        <v>107710</v>
+        <v>107712</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>135651003</v>
       </c>
       <c r="B38" t="n">
-        <v>107710</v>
+        <v>107712</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>135651004</v>
       </c>
       <c r="B39" t="n">
-        <v>107710</v>
+        <v>107712</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>135651008</v>
       </c>
       <c r="B40" t="n">
-        <v>107710</v>
+        <v>107712</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -2451,7 +2451,7 @@
         <v>135650961</v>
       </c>
       <c r="B18" t="n">
-        <v>108311</v>
+        <v>108312</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>135650968</v>
       </c>
       <c r="B19" t="n">
-        <v>108311</v>
+        <v>108312</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>135650972</v>
       </c>
       <c r="B20" t="n">
-        <v>108311</v>
+        <v>108312</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>135651005</v>
       </c>
       <c r="B21" t="n">
-        <v>108311</v>
+        <v>108312</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>135650965</v>
       </c>
       <c r="B22" t="n">
-        <v>110274</v>
+        <v>110275</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>135650976</v>
       </c>
       <c r="B23" t="n">
-        <v>110274</v>
+        <v>110275</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>135650979</v>
       </c>
       <c r="B24" t="n">
-        <v>110274</v>
+        <v>110275</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>135650983</v>
       </c>
       <c r="B25" t="n">
-        <v>110274</v>
+        <v>110275</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>135650987</v>
       </c>
       <c r="B26" t="n">
-        <v>110274</v>
+        <v>110275</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>135650967</v>
       </c>
       <c r="B27" t="n">
-        <v>107712</v>
+        <v>107713</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>135650969</v>
       </c>
       <c r="B28" t="n">
-        <v>107712</v>
+        <v>107713</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>135650970</v>
       </c>
       <c r="B29" t="n">
-        <v>107712</v>
+        <v>107713</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>135650973</v>
       </c>
       <c r="B30" t="n">
-        <v>107712</v>
+        <v>107713</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>135650974</v>
       </c>
       <c r="B31" t="n">
-        <v>107712</v>
+        <v>107713</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>135650980</v>
       </c>
       <c r="B32" t="n">
-        <v>107712</v>
+        <v>107713</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>135650982</v>
       </c>
       <c r="B33" t="n">
-        <v>107712</v>
+        <v>107713</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>135650986</v>
       </c>
       <c r="B34" t="n">
-        <v>107712</v>
+        <v>107713</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>135650998</v>
       </c>
       <c r="B35" t="n">
-        <v>107712</v>
+        <v>107713</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>135650999</v>
       </c>
       <c r="B36" t="n">
-        <v>107712</v>
+        <v>107713</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>135651002</v>
       </c>
       <c r="B37" t="n">
-        <v>107712</v>
+        <v>107713</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>135651003</v>
       </c>
       <c r="B38" t="n">
-        <v>107712</v>
+        <v>107713</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>135651004</v>
       </c>
       <c r="B39" t="n">
-        <v>107712</v>
+        <v>107713</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>135651008</v>
       </c>
       <c r="B40" t="n">
-        <v>107712</v>
+        <v>107713</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -2101,7 +2101,7 @@
         <v>135651157</v>
       </c>
       <c r="B15" t="n">
-        <v>43311</v>
+        <v>43312</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>135650961</v>
       </c>
       <c r="B18" t="n">
-        <v>108312</v>
+        <v>108313</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>135650968</v>
       </c>
       <c r="B19" t="n">
-        <v>108312</v>
+        <v>108313</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>135650972</v>
       </c>
       <c r="B20" t="n">
-        <v>108312</v>
+        <v>108313</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>135651005</v>
       </c>
       <c r="B21" t="n">
-        <v>108312</v>
+        <v>108313</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>135650965</v>
       </c>
       <c r="B22" t="n">
-        <v>110275</v>
+        <v>110276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>135650976</v>
       </c>
       <c r="B23" t="n">
-        <v>110275</v>
+        <v>110276</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>135650979</v>
       </c>
       <c r="B24" t="n">
-        <v>110275</v>
+        <v>110276</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>135650983</v>
       </c>
       <c r="B25" t="n">
-        <v>110275</v>
+        <v>110276</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>135650987</v>
       </c>
       <c r="B26" t="n">
-        <v>110275</v>
+        <v>110276</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>135650967</v>
       </c>
       <c r="B27" t="n">
-        <v>107713</v>
+        <v>107714</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>135650969</v>
       </c>
       <c r="B28" t="n">
-        <v>107713</v>
+        <v>107714</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>135650970</v>
       </c>
       <c r="B29" t="n">
-        <v>107713</v>
+        <v>107714</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>135650973</v>
       </c>
       <c r="B30" t="n">
-        <v>107713</v>
+        <v>107714</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>135650974</v>
       </c>
       <c r="B31" t="n">
-        <v>107713</v>
+        <v>107714</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>135650980</v>
       </c>
       <c r="B32" t="n">
-        <v>107713</v>
+        <v>107714</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>135650982</v>
       </c>
       <c r="B33" t="n">
-        <v>107713</v>
+        <v>107714</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>135650986</v>
       </c>
       <c r="B34" t="n">
-        <v>107713</v>
+        <v>107714</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>135650998</v>
       </c>
       <c r="B35" t="n">
-        <v>107713</v>
+        <v>107714</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>135650999</v>
       </c>
       <c r="B36" t="n">
-        <v>107713</v>
+        <v>107714</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>135651002</v>
       </c>
       <c r="B37" t="n">
-        <v>107713</v>
+        <v>107714</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>135651003</v>
       </c>
       <c r="B38" t="n">
-        <v>107713</v>
+        <v>107714</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>135651004</v>
       </c>
       <c r="B39" t="n">
-        <v>107713</v>
+        <v>107714</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>135651008</v>
       </c>
       <c r="B40" t="n">
-        <v>107713</v>
+        <v>107714</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 63872-2021 artfynd.xlsx
+++ b/artfynd/A 63872-2021 artfynd.xlsx
@@ -2451,7 +2451,7 @@
         <v>135650961</v>
       </c>
       <c r="B18" t="n">
-        <v>108313</v>
+        <v>108319</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>135650968</v>
       </c>
       <c r="B19" t="n">
-        <v>108313</v>
+        <v>108319</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>135650972</v>
       </c>
       <c r="B20" t="n">
-        <v>108313</v>
+        <v>108319</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>135651005</v>
       </c>
       <c r="B21" t="n">
-        <v>108313</v>
+        <v>108319</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>135650965</v>
       </c>
       <c r="B22" t="n">
-        <v>110276</v>
+        <v>110282</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>135650976</v>
       </c>
       <c r="B23" t="n">
-        <v>110276</v>
+        <v>110282</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>135650979</v>
       </c>
       <c r="B24" t="n">
-        <v>110276</v>
+        <v>110282</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>135650983</v>
       </c>
       <c r="B25" t="n">
-        <v>110276</v>
+        <v>110282</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>135650987</v>
       </c>
       <c r="B26" t="n">
-        <v>110276</v>
+        <v>110282</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>135650967</v>
       </c>
       <c r="B27" t="n">
-        <v>107714</v>
+        <v>107720</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>135650969</v>
       </c>
       <c r="B28" t="n">
-        <v>107714</v>
+        <v>107720</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>135650970</v>
       </c>
       <c r="B29" t="n">
-        <v>107714</v>
+        <v>107720</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>135650973</v>
       </c>
       <c r="B30" t="n">
-        <v>107714</v>
+        <v>107720</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>135650974</v>
       </c>
       <c r="B31" t="n">
-        <v>107714</v>
+        <v>107720</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>135650980</v>
       </c>
       <c r="B32" t="n">
-        <v>107714</v>
+        <v>107720</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>135650982</v>
       </c>
       <c r="B33" t="n">
-        <v>107714</v>
+        <v>107720</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>135650986</v>
       </c>
       <c r="B34" t="n">
-        <v>107714</v>
+        <v>107720</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>135650998</v>
       </c>
       <c r="B35" t="n">
-        <v>107714</v>
+        <v>107720</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>135650999</v>
       </c>
       <c r="B36" t="n">
-        <v>107714</v>
+        <v>107720</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>135651002</v>
       </c>
       <c r="B37" t="n">
-        <v>107714</v>
+        <v>107720</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>135651003</v>
       </c>
       <c r="B38" t="n">
-        <v>107714</v>
+        <v>107720</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>135651004</v>
       </c>
       <c r="B39" t="n">
-        <v>107714</v>
+        <v>107720</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>135651008</v>
       </c>
       <c r="B40" t="n">
-        <v>107714</v>
+        <v>107720</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
